--- a/fixtures/xlsx/representative/structured.xlsx
+++ b/fixtures/xlsx/representative/structured.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" customAttr="keep">
   <sheetData>
     <row r="1">
       <c r="A1">
